--- a/examples/trades_example.xlsx
+++ b/examples/trades_example.xlsx
@@ -10,10 +10,11 @@
     <sheet name="Config" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Market" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Curve" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="VolSurface" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Correlation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="NettingSets" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Trades" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="FX" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="VolSurface" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Correlation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NettingSets" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Trades" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,6 +545,18 @@
       </c>
       <c r="B11" t="n">
         <v>201</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>reporting_ccy</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -557,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,6 +604,11 @@
           <t>bbg_ticker</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ccy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -617,6 +635,11 @@
           <t>AAPL US Equity</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -641,6 +664,42 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>SPX Index</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STOCK_CA</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>67.44</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TOU CN Equity</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CAD</t>
         </is>
       </c>
     </row>
@@ -655,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,6 +728,11 @@
           <t>zero_rate</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ccy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -679,6 +743,11 @@
       <c r="B2" t="n">
         <v>0.041</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -689,6 +758,11 @@
       <c r="B3" t="n">
         <v>0.0405</v>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -699,6 +773,11 @@
       <c r="B4" t="n">
         <v>0.0395</v>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -709,6 +788,11 @@
       <c r="B5" t="n">
         <v>0.038</v>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -719,6 +803,11 @@
       <c r="B6" t="n">
         <v>0.0365</v>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -729,6 +818,11 @@
       <c r="B7" t="n">
         <v>0.036</v>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -739,6 +833,11 @@
       <c r="B8" t="n">
         <v>0.0362</v>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -748,6 +847,131 @@
       </c>
       <c r="B9" t="n">
         <v>0.0375</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0228</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -761,569 +985,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>underlying</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>tenor</t>
+          <t>bbg_ticker</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>moneyness</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>vol</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STOCK_A</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>USDCAD Curncy</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.285</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.275</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6M</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.345</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>6M</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.315</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>6M</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.285</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>6M</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>6M</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.265</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1Y</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1Y</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1Y</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1Y</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.265</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1Y</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2Y</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.335</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2Y</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.305</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2Y</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.275</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2Y</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2Y</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.255</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.255</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STOCK_A</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.25</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -1337,23 +1031,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>underlying1</t>
+          <t>underlying</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>underlying2</t>
+          <t>tenor</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>rho</t>
+          <t>moneyness</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>vol</t>
         </is>
       </c>
     </row>
@@ -1365,11 +1064,536 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INDEX_X</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.285</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.275</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.285</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.265</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.265</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.335</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.305</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.275</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.255</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.255</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STOCK_A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1383,201 +1607,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>netting_set</t>
+          <t>underlying1</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>counterparty</t>
+          <t>underlying2</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>collateralized</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>threshold_cp</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>threshold_bank</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>mta</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ia_received</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ia_posted</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>ia_posted_segregated</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>mpor_days</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>rounding</t>
+          <t>rho</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NS_ALPHA</t>
+          <t>STOCK_A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alpha Fund</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NS_BETA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Beta Capital</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NS_GAMMA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Gamma Partners</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NS_DELTA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Delta Pension</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>500000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>INDEX_X</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1590,7 +1653,269 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>netting_set</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>counterparty</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>collateralized</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>threshold_cp</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>threshold_bank</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mta</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ia_received</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ia_posted</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ia_posted_segregated</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>mpor_days</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>rounding</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>csa_ccy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NS_ALPHA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Alpha Fund</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NS_BETA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Beta Capital</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NS_GAMMA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gamma Partners</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NS_DELTA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Delta Pension</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NS_EPSILON</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Epsilon Asset Mgmt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1000000000000000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>400000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2481,6 +2806,70 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NS_EPSILON</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OPTION</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>STOCK_CA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>75</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2027-02-27</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>CAD stock call under a CAD CSA (C$ thresholds), reported in USD</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
